--- a/AAII_Financials/Yearly/TRS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TRS_YR_FIN.xlsx
@@ -3125,10 +3125,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>519300</v>
+        <v>501000</v>
       </c>
       <c r="E61" s="3">
-        <v>431300</v>
+        <v>428400</v>
       </c>
       <c r="F61" s="3">
         <v>435400</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>58900</v>
+        <v>77100</v>
       </c>
       <c r="E62" s="3">
-        <v>48600</v>
+        <v>51500</v>
       </c>
       <c r="F62" s="3">
         <v>40600</v>
